--- a/VerveStacks_POL_grids_kan/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5408ADFE-CD55-4C96-BB16-5DF8193725E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D976E044-B964-4D23-96BA-AA80F0D84C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{779EBA8A-E0BE-4A42-A9FE-BD1952DD0641}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{162BC542-19F4-4A40-AF00-14A83F5D5072}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3883,7 +3883,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BBE226B-6203-45BB-BBB5-6CE4C342CDB2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EB4AA36-9550-400C-A076-E2E49CCBF774}">
   <dimension ref="B9:T187"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -13869,7 +13869,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B66236-B477-4355-9DB2-41CE0B292F98}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEBD7215-D7E3-40B1-A51D-7AF68B3F8BD4}">
   <dimension ref="B9:T151"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20684,7 +20684,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7216B3F-E56E-4CB0-B018-BD2090AA4F78}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3490934-0EA1-4F87-94BC-F46DA7FE8BA8}">
   <dimension ref="B9:T382"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -32755,7 +32755,7 @@
         <v>318</v>
       </c>
       <c r="P238" t="s">
-        <v>601</v>
+        <v>400</v>
       </c>
       <c r="Q238" t="s">
         <v>387</v>
@@ -32811,7 +32811,7 @@
         <v>318</v>
       </c>
       <c r="P239" t="s">
-        <v>400</v>
+        <v>601</v>
       </c>
       <c r="Q239" t="s">
         <v>387</v>
@@ -32923,7 +32923,7 @@
         <v>321</v>
       </c>
       <c r="P241" t="s">
-        <v>601</v>
+        <v>400</v>
       </c>
       <c r="Q241" t="s">
         <v>387</v>
@@ -32979,7 +32979,7 @@
         <v>321</v>
       </c>
       <c r="P242" t="s">
-        <v>400</v>
+        <v>601</v>
       </c>
       <c r="Q242" t="s">
         <v>387</v>
@@ -33987,7 +33987,7 @@
         <v>354</v>
       </c>
       <c r="P260" t="s">
-        <v>601</v>
+        <v>400</v>
       </c>
       <c r="Q260" t="s">
         <v>387</v>
@@ -34043,7 +34043,7 @@
         <v>354</v>
       </c>
       <c r="P261" t="s">
-        <v>400</v>
+        <v>601</v>
       </c>
       <c r="Q261" t="s">
         <v>387</v>
@@ -34267,7 +34267,7 @@
         <v>361</v>
       </c>
       <c r="P265" t="s">
-        <v>601</v>
+        <v>400</v>
       </c>
       <c r="Q265" t="s">
         <v>387</v>
@@ -34323,7 +34323,7 @@
         <v>361</v>
       </c>
       <c r="P266" t="s">
-        <v>400</v>
+        <v>601</v>
       </c>
       <c r="Q266" t="s">
         <v>387</v>
@@ -34641,7 +34641,7 @@
         <v>33</v>
       </c>
       <c r="L272">
-        <v>0.32007950711570904</v>
+        <v>0.32007950711570915</v>
       </c>
       <c r="N272" t="s">
         <v>385</v>
@@ -34688,7 +34688,7 @@
         <v>33</v>
       </c>
       <c r="L273">
-        <v>0.32007950711570904</v>
+        <v>0.32007950711570915</v>
       </c>
       <c r="N273" t="s">
         <v>385</v>
@@ -34735,7 +34735,7 @@
         <v>33</v>
       </c>
       <c r="L274">
-        <v>0.32007950711570904</v>
+        <v>0.32007950711570915</v>
       </c>
       <c r="N274" t="s">
         <v>385</v>
@@ -34744,7 +34744,7 @@
         <v>376</v>
       </c>
       <c r="P274" t="s">
-        <v>400</v>
+        <v>601</v>
       </c>
       <c r="Q274" t="s">
         <v>387</v>
@@ -34800,7 +34800,7 @@
         <v>376</v>
       </c>
       <c r="P275" t="s">
-        <v>601</v>
+        <v>400</v>
       </c>
       <c r="Q275" t="s">
         <v>387</v>
@@ -38566,7 +38566,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5878010-3C73-4CF2-8923-E99810417CB9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD7209E-F620-4CFE-B0AA-108E4A8E1FC0}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_POL_grids_kan/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{491B12A9-8D05-4D15-A28F-47C9A2642C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{420C3089-EA01-47B8-ABCD-64EC8A14C06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DDD500BA-4C97-4535-B174-DE84AE00B9A1}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5E9A5C8B-F241-4A9A-B6CE-621559566D26}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3892,7 +3892,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3141FA6-4102-4C38-B71E-5EBFE67F6C64}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA7AD9AA-FACB-4188-892C-3B1278137613}">
   <dimension ref="B9:V187"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14946,7 +14946,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3786C409-1FDA-4137-84C2-438D374E339F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{678B26CE-44BB-45DD-804A-98914E1F5B26}">
   <dimension ref="B9:V151"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -22490,7 +22490,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1ADF969-BD1E-4401-81BA-54FE07203EEF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B2C4702-8A75-4CF7-96CF-B4C9F0A49607}">
   <dimension ref="B9:V382"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -35935,7 +35935,7 @@
         <v>14</v>
       </c>
       <c r="R238" t="s">
-        <v>402</v>
+        <v>603</v>
       </c>
       <c r="S238" t="s">
         <v>389</v>
@@ -35997,7 +35997,7 @@
         <v>14</v>
       </c>
       <c r="R239" t="s">
-        <v>603</v>
+        <v>402</v>
       </c>
       <c r="S239" t="s">
         <v>389</v>
@@ -36121,7 +36121,7 @@
         <v>14</v>
       </c>
       <c r="R241" t="s">
-        <v>603</v>
+        <v>402</v>
       </c>
       <c r="S241" t="s">
         <v>389</v>
@@ -36183,7 +36183,7 @@
         <v>14</v>
       </c>
       <c r="R242" t="s">
-        <v>402</v>
+        <v>603</v>
       </c>
       <c r="S242" t="s">
         <v>389</v>
@@ -37113,7 +37113,7 @@
         <v>14</v>
       </c>
       <c r="R257" t="s">
-        <v>402</v>
+        <v>603</v>
       </c>
       <c r="S257" t="s">
         <v>389</v>
@@ -37175,7 +37175,7 @@
         <v>14</v>
       </c>
       <c r="R258" t="s">
-        <v>603</v>
+        <v>402</v>
       </c>
       <c r="S258" t="s">
         <v>389</v>
@@ -37609,7 +37609,7 @@
         <v>14</v>
       </c>
       <c r="R265" t="s">
-        <v>603</v>
+        <v>402</v>
       </c>
       <c r="S265" t="s">
         <v>389</v>
@@ -37671,7 +37671,7 @@
         <v>14</v>
       </c>
       <c r="R266" t="s">
-        <v>402</v>
+        <v>603</v>
       </c>
       <c r="S266" t="s">
         <v>389</v>
@@ -38022,7 +38022,7 @@
         <v>33</v>
       </c>
       <c r="M272">
-        <v>0.31276535128895466</v>
+        <v>0.31276535128895461</v>
       </c>
       <c r="O272" t="s">
         <v>387</v>
@@ -38075,7 +38075,7 @@
         <v>33</v>
       </c>
       <c r="M273">
-        <v>0.31276535128895466</v>
+        <v>0.31276535128895461</v>
       </c>
       <c r="O273" t="s">
         <v>387</v>
@@ -38128,7 +38128,7 @@
         <v>33</v>
       </c>
       <c r="M274">
-        <v>0.31276535128895466</v>
+        <v>0.31276535128895461</v>
       </c>
       <c r="O274" t="s">
         <v>387</v>
@@ -38140,7 +38140,7 @@
         <v>14</v>
       </c>
       <c r="R274" t="s">
-        <v>603</v>
+        <v>402</v>
       </c>
       <c r="S274" t="s">
         <v>389</v>
@@ -38202,7 +38202,7 @@
         <v>14</v>
       </c>
       <c r="R275" t="s">
-        <v>402</v>
+        <v>603</v>
       </c>
       <c r="S275" t="s">
         <v>389</v>
@@ -42289,7 +42289,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4DA2B36-23FB-44DA-9D72-BF5FF07C419D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E91F107A-A78B-47DC-9406-82FDF260B835}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_POL_grids_kan/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C40D8E9-0629-4806-9353-B0B21F990DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C16C7AAB-FF6D-4B05-B416-7FA4D3B620F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{626A128B-661A-4C8B-839A-5D253E504090}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C08B6675-2E37-49D4-8FFE-FFA12CEA2793}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3913,7 +3913,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B84ADDF9-0324-9368-8E00-D10B549C20F0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FF9BCE9-A74A-BEA8-C101-56835A7DB0EE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3968,7 +3968,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D56A3F5-1802-0017-E7B7-DF560AF713C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DF8FB3B-59AA-1234-4668-AEF71429F950}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4023,7 +4023,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED48FB42-0AFE-1C6A-5BC1-FB30FB04EE65}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92E684BA-4D3A-1D55-05E0-67F33607FD79}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4374,7 +4374,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{969B5F15-7329-46FD-8503-11D7FA687EDD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8387CE4-472B-4D71-936A-30680FE03299}">
   <dimension ref="A1:V187"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -15462,7 +15462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63E153B5-DA2D-4B27-B647-3A09E022EE51}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB5BD33B-90D3-465C-A65A-0917FA06B59F}">
   <dimension ref="A1:W157"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -23655,7 +23655,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B91662-C53C-49CE-B80E-A41DF3E208C6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1441EFA5-E04E-4537-BFE2-9875B674D5D8}">
   <dimension ref="A1:W388"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -37583,7 +37583,7 @@
         <v>15</v>
       </c>
       <c r="S233" s="4" t="s">
-        <v>630</v>
+        <v>428</v>
       </c>
       <c r="T233" s="4" t="s">
         <v>413</v>
@@ -37646,7 +37646,7 @@
         <v>15</v>
       </c>
       <c r="S234" s="9" t="s">
-        <v>428</v>
+        <v>630</v>
       </c>
       <c r="T234" s="9" t="s">
         <v>413</v>
@@ -38213,7 +38213,7 @@
         <v>15</v>
       </c>
       <c r="S243" s="4" t="s">
-        <v>428</v>
+        <v>630</v>
       </c>
       <c r="T243" s="4" t="s">
         <v>413</v>
@@ -38276,7 +38276,7 @@
         <v>15</v>
       </c>
       <c r="S244" s="9" t="s">
-        <v>630</v>
+        <v>428</v>
       </c>
       <c r="T244" s="9" t="s">
         <v>413</v>
@@ -38402,7 +38402,7 @@
         <v>15</v>
       </c>
       <c r="S246" s="9" t="s">
-        <v>630</v>
+        <v>428</v>
       </c>
       <c r="T246" s="9" t="s">
         <v>413</v>
@@ -38465,7 +38465,7 @@
         <v>15</v>
       </c>
       <c r="S247" s="4" t="s">
-        <v>428</v>
+        <v>630</v>
       </c>
       <c r="T247" s="4" t="s">
         <v>413</v>
@@ -39599,7 +39599,7 @@
         <v>15</v>
       </c>
       <c r="S265" s="4" t="s">
-        <v>428</v>
+        <v>630</v>
       </c>
       <c r="T265" s="4" t="s">
         <v>413</v>
@@ -39662,7 +39662,7 @@
         <v>15</v>
       </c>
       <c r="S266" s="9" t="s">
-        <v>630</v>
+        <v>428</v>
       </c>
       <c r="T266" s="9" t="s">
         <v>413</v>
@@ -40463,7 +40463,7 @@
         <v>15</v>
       </c>
       <c r="S279" s="4" t="s">
-        <v>630</v>
+        <v>428</v>
       </c>
       <c r="T279" s="4" t="s">
         <v>413</v>
@@ -40526,7 +40526,7 @@
         <v>15</v>
       </c>
       <c r="S280" s="9" t="s">
-        <v>428</v>
+        <v>630</v>
       </c>
       <c r="T280" s="9" t="s">
         <v>413</v>
@@ -44775,7 +44775,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07C442B7-BD84-47E5-8D68-75AF8431526E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{843E246B-D9B0-4F57-AE7A-4CB7525D7CA9}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_POL_grids_kan/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB418379-182A-460F-BCB4-FC7DE8409451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A82C5279-B465-44B7-A513-1AFAD5D43E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4CB42F38-0144-4309-BF46-D49C316EC9F6}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DD568494-A513-4FBB-B18D-FD4F6F4FD4EA}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -4111,7 +4111,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{591432F4-8C21-4B63-9C4C-DF56D135A389}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDA63AB4-70AB-4D65-8D06-6F640225FD67}">
   <dimension ref="B9:V187"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15165,7 +15165,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31CCAFEE-8DBB-459D-BB53-1CB8CA84B69D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E4611DE-F442-4CE6-AF34-85679CBD215D}">
   <dimension ref="B9:W157"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23078,7 +23078,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B45081-E554-455D-9466-D34E46D997F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8DA6E82-BD2C-49C3-B463-89FD6590103E}">
   <dimension ref="B9:W388"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -37268,7 +37268,7 @@
         <v>15</v>
       </c>
       <c r="S243" t="s">
-        <v>427</v>
+        <v>629</v>
       </c>
       <c r="T243" t="s">
         <v>412</v>
@@ -37330,7 +37330,7 @@
         <v>15</v>
       </c>
       <c r="S244" t="s">
-        <v>629</v>
+        <v>427</v>
       </c>
       <c r="T244" t="s">
         <v>412</v>
@@ -37454,7 +37454,7 @@
         <v>15</v>
       </c>
       <c r="S246" t="s">
-        <v>629</v>
+        <v>427</v>
       </c>
       <c r="T246" t="s">
         <v>412</v>
@@ -37516,7 +37516,7 @@
         <v>15</v>
       </c>
       <c r="S247" t="s">
-        <v>427</v>
+        <v>629</v>
       </c>
       <c r="T247" t="s">
         <v>412</v>
@@ -39355,7 +39355,7 @@
         <v>33</v>
       </c>
       <c r="N277">
-        <v>0.31276535128895466</v>
+        <v>0.31276535128895461</v>
       </c>
       <c r="P277" t="s">
         <v>410</v>
@@ -39408,7 +39408,7 @@
         <v>33</v>
       </c>
       <c r="N278">
-        <v>0.31276535128895466</v>
+        <v>0.31276535128895461</v>
       </c>
       <c r="P278" t="s">
         <v>410</v>
@@ -39461,7 +39461,7 @@
         <v>33</v>
       </c>
       <c r="N279">
-        <v>0.31276535128895466</v>
+        <v>0.31276535128895461</v>
       </c>
       <c r="P279" t="s">
         <v>410</v>
@@ -43666,7 +43666,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B46E8AC1-B09F-4E16-B250-6E9D202FC47F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8CDE611-B374-4AD5-B5C4-4C29DAEC5E64}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_POL_grids_kan/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A82C5279-B465-44B7-A513-1AFAD5D43E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0DE8A24-9E75-4D28-A3C7-441978E98C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DD568494-A513-4FBB-B18D-FD4F6F4FD4EA}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9F597A80-9E21-4663-84C1-BD28EFD87908}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -4111,7 +4111,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDA63AB4-70AB-4D65-8D06-6F640225FD67}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD9DC4CD-47D7-4836-98A5-1F363C06E447}">
   <dimension ref="B9:V187"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15165,7 +15165,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E4611DE-F442-4CE6-AF34-85679CBD215D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDEB63F0-0123-4A66-AC4E-1E46A55B0C5D}">
   <dimension ref="B9:W157"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23078,7 +23078,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8DA6E82-BD2C-49C3-B463-89FD6590103E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF77F75-6AEA-4AED-B76D-9B22B1F45B52}">
   <dimension ref="B9:W388"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43666,7 +43666,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8CDE611-B374-4AD5-B5C4-4C29DAEC5E64}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A0A6AC0-0616-4AF0-BF0B-14A356C47FDB}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_POL_grids_kan/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan/vt_vervestacks_POL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0DE8A24-9E75-4D28-A3C7-441978E98C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DBCC92B-3284-4C08-AF43-B59C8047F7FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9F597A80-9E21-4663-84C1-BD28EFD87908}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{950F7191-5807-4A64-8E99-3F55D24FFAE5}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -4111,7 +4111,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD9DC4CD-47D7-4836-98A5-1F363C06E447}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F844FB0E-1227-403A-9CA4-3BDAF8537147}">
   <dimension ref="B9:V187"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15165,7 +15165,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDEB63F0-0123-4A66-AC4E-1E46A55B0C5D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B495903-5802-47A8-868A-7BB37DDF7883}">
   <dimension ref="B9:W157"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15274,7 +15274,7 @@
         <v>3.1500000000000004</v>
       </c>
       <c r="L11">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M11">
         <v>50</v>
@@ -15336,7 +15336,7 @@
         <v>3.1500000000000004</v>
       </c>
       <c r="L12">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M12">
         <v>50</v>
@@ -21944,7 +21944,7 @@
         <v>5.04</v>
       </c>
       <c r="L127">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M127">
         <v>40</v>
@@ -21982,7 +21982,7 @@
         <v>8.19</v>
       </c>
       <c r="L128">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M128">
         <v>40</v>
@@ -23078,7 +23078,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF77F75-6AEA-4AED-B76D-9B22B1F45B52}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5825902D-8C42-43F6-9989-4ACBB9DBA55D}">
   <dimension ref="B9:W388"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23246,7 +23246,7 @@
         <v>9.240000000000002</v>
       </c>
       <c r="L12">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M12">
         <v>50</v>
@@ -23308,7 +23308,7 @@
         <v>9.240000000000002</v>
       </c>
       <c r="L13">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M13">
         <v>50</v>
@@ -23370,7 +23370,7 @@
         <v>9.240000000000002</v>
       </c>
       <c r="L14">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M14">
         <v>77</v>
@@ -23432,7 +23432,7 @@
         <v>10.08</v>
       </c>
       <c r="L15">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M15">
         <v>102</v>
@@ -23553,7 +23553,7 @@
         <v>9.240000000000002</v>
       </c>
       <c r="L17">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M17">
         <v>72</v>
@@ -23615,7 +23615,7 @@
         <v>10.08</v>
       </c>
       <c r="L18">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M18">
         <v>50</v>
@@ -23677,7 +23677,7 @@
         <v>9.240000000000002</v>
       </c>
       <c r="L19">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M19">
         <v>50</v>
@@ -23857,7 +23857,7 @@
         <v>10.08</v>
       </c>
       <c r="L22">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M22">
         <v>50</v>
@@ -23978,7 +23978,7 @@
         <v>10.08</v>
       </c>
       <c r="L24">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M24">
         <v>50</v>
@@ -24099,7 +24099,7 @@
         <v>10.08</v>
       </c>
       <c r="L26">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M26">
         <v>50</v>
@@ -24338,7 +24338,7 @@
         <v>10.08</v>
       </c>
       <c r="L30">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M30">
         <v>50</v>
@@ -24636,7 +24636,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L35">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M35">
         <v>80</v>
@@ -24698,7 +24698,7 @@
         <v>5.25</v>
       </c>
       <c r="L36">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M36">
         <v>47</v>
@@ -24760,7 +24760,7 @@
         <v>5.25</v>
       </c>
       <c r="L37">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M37">
         <v>47</v>
@@ -24822,7 +24822,7 @@
         <v>5.25</v>
       </c>
       <c r="L38">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M38">
         <v>47</v>
@@ -24884,7 +24884,7 @@
         <v>5.25</v>
       </c>
       <c r="L39">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M39">
         <v>47</v>
@@ -24946,7 +24946,7 @@
         <v>5.25</v>
       </c>
       <c r="L40">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M40">
         <v>47</v>
@@ -25008,7 +25008,7 @@
         <v>5.25</v>
       </c>
       <c r="L41">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M41">
         <v>48</v>
@@ -25070,7 +25070,7 @@
         <v>5.25</v>
       </c>
       <c r="L42">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M42">
         <v>47</v>
@@ -25132,7 +25132,7 @@
         <v>5.25</v>
       </c>
       <c r="L43">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M43">
         <v>48</v>
@@ -25194,7 +25194,7 @@
         <v>5.25</v>
       </c>
       <c r="L44">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M44">
         <v>48</v>
@@ -25256,7 +25256,7 @@
         <v>5.25</v>
       </c>
       <c r="L45">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M45">
         <v>48</v>
@@ -25318,7 +25318,7 @@
         <v>5.25</v>
       </c>
       <c r="L46">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M46">
         <v>48</v>
@@ -25380,7 +25380,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L47">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M47">
         <v>74</v>
@@ -25442,7 +25442,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L48">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M48">
         <v>64</v>
@@ -25504,7 +25504,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L49">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M49">
         <v>58</v>
@@ -25566,7 +25566,7 @@
         <v>6.3000000000000007</v>
       </c>
       <c r="L50">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M50">
         <v>50</v>
@@ -25628,7 +25628,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L51">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M51">
         <v>54</v>
@@ -25690,7 +25690,7 @@
         <v>6.3000000000000007</v>
       </c>
       <c r="L52">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M52">
         <v>54</v>
@@ -25752,7 +25752,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L53">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M53">
         <v>54</v>
@@ -25814,7 +25814,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L54">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M54">
         <v>52</v>
@@ -25876,7 +25876,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L55">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M55">
         <v>52</v>
@@ -25938,7 +25938,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L56">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M56">
         <v>17</v>
@@ -26236,7 +26236,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L61">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M61">
         <v>57</v>
@@ -26298,7 +26298,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L62">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M62">
         <v>52</v>
@@ -26360,7 +26360,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L63">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M63">
         <v>46</v>
@@ -26422,7 +26422,7 @@
         <v>5.7750000000000012</v>
       </c>
       <c r="L64">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M64">
         <v>36</v>
@@ -26484,7 +26484,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L65">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M65">
         <v>44</v>
@@ -26546,7 +26546,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L66">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M66">
         <v>40</v>
@@ -26608,7 +26608,7 @@
         <v>6.3000000000000007</v>
       </c>
       <c r="L67">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M67">
         <v>52</v>
@@ -26670,7 +26670,7 @@
         <v>6.3000000000000007</v>
       </c>
       <c r="L68">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M68">
         <v>47</v>
@@ -26732,7 +26732,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L69">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M69">
         <v>57</v>
@@ -26794,7 +26794,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L70">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M70">
         <v>57</v>
@@ -26856,7 +26856,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L71">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M71">
         <v>78</v>
@@ -26918,7 +26918,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L72">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M72">
         <v>78</v>
@@ -26980,7 +26980,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L73">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M73">
         <v>78</v>
@@ -27042,7 +27042,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L74">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M74">
         <v>78</v>
@@ -27104,7 +27104,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L75">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M75">
         <v>77</v>
@@ -27166,7 +27166,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L76">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M76">
         <v>77</v>
@@ -27228,7 +27228,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L77">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M77">
         <v>56</v>
@@ -27290,7 +27290,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L78">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M78">
         <v>64</v>
@@ -27942,7 +27942,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L89">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M89">
         <v>60</v>
@@ -28004,7 +28004,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L90">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M90">
         <v>52</v>
@@ -28066,7 +28066,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L91">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M91">
         <v>45</v>
@@ -28364,7 +28364,7 @@
         <v>6.3000000000000007</v>
       </c>
       <c r="L96">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M96">
         <v>57</v>
@@ -28426,7 +28426,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L97">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M97">
         <v>57</v>
@@ -28488,7 +28488,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L98">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M98">
         <v>57</v>
@@ -28550,7 +28550,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L99">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M99">
         <v>57</v>
@@ -28612,7 +28612,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L100">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M100">
         <v>48</v>
@@ -28674,7 +28674,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L101">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M101">
         <v>47</v>
@@ -28736,7 +28736,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L102">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M102">
         <v>33</v>
@@ -29034,7 +29034,7 @@
         <v>6.3000000000000007</v>
       </c>
       <c r="L107">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M107">
         <v>97</v>
@@ -29214,7 +29214,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L110">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M110">
         <v>83</v>
@@ -29453,7 +29453,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L114">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M114">
         <v>76</v>
@@ -29515,7 +29515,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L115">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M115">
         <v>76</v>
@@ -29577,7 +29577,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L116">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M116">
         <v>76</v>
@@ -29639,7 +29639,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L117">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M117">
         <v>76</v>
@@ -29701,7 +29701,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L118">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M118">
         <v>73</v>
@@ -29763,7 +29763,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L119">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M119">
         <v>73</v>
@@ -29825,7 +29825,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L120">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M120">
         <v>72</v>
@@ -29887,7 +29887,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L121">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M121">
         <v>94</v>
@@ -29949,7 +29949,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L122">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M122">
         <v>94</v>
@@ -30011,7 +30011,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L123">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M123">
         <v>40</v>
@@ -30073,7 +30073,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L124">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M124">
         <v>34</v>
@@ -30135,7 +30135,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L125">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M125">
         <v>27</v>
@@ -30197,7 +30197,7 @@
         <v>6.3000000000000007</v>
       </c>
       <c r="L126">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M126">
         <v>90</v>
@@ -30259,7 +30259,7 @@
         <v>6.3000000000000007</v>
       </c>
       <c r="L127">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M127">
         <v>90</v>
@@ -30321,7 +30321,7 @@
         <v>6.3000000000000007</v>
       </c>
       <c r="L128">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M128">
         <v>85</v>
@@ -30501,7 +30501,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L131">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M131">
         <v>48</v>
@@ -30563,7 +30563,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L132">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M132">
         <v>48</v>
@@ -30625,7 +30625,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L133">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M133">
         <v>49</v>
@@ -30687,7 +30687,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L134">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M134">
         <v>49</v>
@@ -30749,7 +30749,7 @@
         <v>6.3000000000000007</v>
       </c>
       <c r="L135">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M135">
         <v>70</v>
@@ -30811,7 +30811,7 @@
         <v>6.3000000000000007</v>
       </c>
       <c r="L136">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M136">
         <v>70</v>
@@ -30873,7 +30873,7 @@
         <v>6.3000000000000007</v>
       </c>
       <c r="L137">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M137">
         <v>70</v>
@@ -30935,7 +30935,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L138">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M138">
         <v>74</v>
@@ -30997,7 +30997,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L139">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M139">
         <v>60</v>
@@ -31059,7 +31059,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L140">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M140">
         <v>60</v>
@@ -31121,7 +31121,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L141">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M141">
         <v>60</v>
@@ -31183,7 +31183,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L142">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M142">
         <v>26</v>
@@ -31245,7 +31245,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L143">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M143">
         <v>26</v>
@@ -31307,7 +31307,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L144">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M144">
         <v>94</v>
@@ -31369,7 +31369,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L145">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M145">
         <v>94</v>
@@ -31431,7 +31431,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L146">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M146">
         <v>94</v>
@@ -31493,7 +31493,7 @@
         <v>6.3000000000000007</v>
       </c>
       <c r="L147">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M147">
         <v>63</v>
@@ -31555,7 +31555,7 @@
         <v>6.3000000000000007</v>
       </c>
       <c r="L148">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M148">
         <v>81</v>
@@ -31617,7 +31617,7 @@
         <v>6.3000000000000007</v>
       </c>
       <c r="L149">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M149">
         <v>50</v>
@@ -31679,7 +31679,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L150">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M150">
         <v>93</v>
@@ -31741,7 +31741,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L151">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M151">
         <v>93</v>
@@ -31803,7 +31803,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L152">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M152">
         <v>92</v>
@@ -31865,7 +31865,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L153">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M153">
         <v>92</v>
@@ -31927,7 +31927,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L154">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M154">
         <v>91</v>
@@ -31989,7 +31989,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L155">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M155">
         <v>91</v>
@@ -32051,7 +32051,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L156">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M156">
         <v>50</v>
@@ -32113,7 +32113,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L157">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M157">
         <v>85</v>
@@ -32175,7 +32175,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L158">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M158">
         <v>75</v>
@@ -32237,7 +32237,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L159">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M159">
         <v>70</v>
@@ -32299,7 +32299,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L160">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M160">
         <v>9</v>
@@ -32361,7 +32361,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L161">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M161">
         <v>70</v>
@@ -32423,7 +32423,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L162">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M162">
         <v>26</v>
@@ -32485,7 +32485,7 @@
         <v>5.25</v>
       </c>
       <c r="L163">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M163">
         <v>81</v>
@@ -32547,7 +32547,7 @@
         <v>6.3000000000000007</v>
       </c>
       <c r="L164">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M164">
         <v>63</v>
@@ -32609,7 +32609,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L165">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M165">
         <v>50</v>
@@ -32671,7 +32671,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L166">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M166">
         <v>98</v>
@@ -32733,7 +32733,7 @@
         <v>6.3000000000000007</v>
       </c>
       <c r="L167">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M167">
         <v>59</v>
@@ -32795,7 +32795,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L168">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M168">
         <v>60</v>
@@ -32857,7 +32857,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L169">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M169">
         <v>50</v>
@@ -32919,7 +32919,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L170">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M170">
         <v>50</v>
@@ -33040,7 +33040,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L172">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M172">
         <v>15</v>
@@ -33102,7 +33102,7 @@
         <v>5.7750000000000004</v>
       </c>
       <c r="L173">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M173">
         <v>26</v>
@@ -33509,7 +33509,7 @@
         <v>3.4650000000000003</v>
       </c>
       <c r="L180">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M180">
         <v>31</v>
@@ -33571,7 +33571,7 @@
         <v>3.4650000000000003</v>
       </c>
       <c r="L181">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M181">
         <v>50</v>
@@ -33633,7 +33633,7 @@
         <v>3.78</v>
       </c>
       <c r="L182">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M182">
         <v>50</v>
@@ -33695,7 +33695,7 @@
         <v>3.4650000000000003</v>
       </c>
       <c r="L183">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M183">
         <v>52</v>
@@ -33757,7 +33757,7 @@
         <v>3.4649999999999999</v>
       </c>
       <c r="L184">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M184">
         <v>50</v>
@@ -33819,7 +33819,7 @@
         <v>3.7799999999999994</v>
       </c>
       <c r="L185">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M185">
         <v>53</v>
@@ -33881,7 +33881,7 @@
         <v>3.78</v>
       </c>
       <c r="L186">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M186">
         <v>50</v>
@@ -33943,7 +33943,7 @@
         <v>3.4650000000000003</v>
       </c>
       <c r="L187">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M187">
         <v>51</v>
@@ -34005,7 +34005,7 @@
         <v>3.4650000000000003</v>
       </c>
       <c r="L188">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M188">
         <v>55</v>
@@ -34067,7 +34067,7 @@
         <v>3.1500000000000004</v>
       </c>
       <c r="L189">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M189">
         <v>50</v>
@@ -34129,7 +34129,7 @@
         <v>3.4650000000000003</v>
       </c>
       <c r="L190">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M190">
         <v>31</v>
@@ -34250,7 +34250,7 @@
         <v>3.1500000000000004</v>
       </c>
       <c r="L192">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M192">
         <v>50</v>
@@ -34312,7 +34312,7 @@
         <v>3.1500000000000004</v>
       </c>
       <c r="L193">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M193">
         <v>50</v>
@@ -34433,7 +34433,7 @@
         <v>3.1500000000000004</v>
       </c>
       <c r="L195">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M195">
         <v>50</v>
@@ -34495,7 +34495,7 @@
         <v>3.1500000000000004</v>
       </c>
       <c r="L196">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M196">
         <v>50</v>
@@ -34616,7 +34616,7 @@
         <v>3.1500000000000004</v>
       </c>
       <c r="L198">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M198">
         <v>50</v>
@@ -34678,7 +34678,7 @@
         <v>3.4650000000000003</v>
       </c>
       <c r="L199">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M199">
         <v>50</v>
@@ -34740,7 +34740,7 @@
         <v>3.4650000000000007</v>
       </c>
       <c r="L200">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M200">
         <v>50</v>
@@ -34802,7 +34802,7 @@
         <v>3.1500000000000008</v>
       </c>
       <c r="L201">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M201">
         <v>50</v>
@@ -34864,7 +34864,7 @@
         <v>4.620000000000001</v>
       </c>
       <c r="L202">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M202">
         <v>40</v>
@@ -34926,7 +34926,7 @@
         <v>4.620000000000001</v>
       </c>
       <c r="L203">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M203">
         <v>40</v>
@@ -34988,7 +34988,7 @@
         <v>7.5075000000000003</v>
       </c>
       <c r="L204">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M204">
         <v>40</v>
@@ -35050,7 +35050,7 @@
         <v>8.19</v>
       </c>
       <c r="L205">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M205">
         <v>48</v>
@@ -35112,7 +35112,7 @@
         <v>8.19</v>
       </c>
       <c r="L206">
-        <v>0.35389999999999999</v>
+        <v>0.58840000000000003</v>
       </c>
       <c r="M206">
         <v>75</v>
@@ -35174,7 +35174,7 @@
         <v>5.67</v>
       </c>
       <c r="L207">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M207">
         <v>50</v>
@@ -35236,7 +35236,7 @@
         <v>5.1975000000000007</v>
       </c>
       <c r="L208">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M208">
         <v>50</v>
@@ -35298,7 +35298,7 @@
         <v>5.1974999999999998</v>
       </c>
       <c r="L209">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M209">
         <v>100</v>
@@ -35360,7 +35360,7 @@
         <v>5.1974999999999998</v>
       </c>
       <c r="L210">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M210">
         <v>97</v>
@@ -35422,7 +35422,7 @@
         <v>5.669999999999999</v>
       </c>
       <c r="L211">
-        <v>0.35189999999999999</v>
+        <v>0.58509999999999995</v>
       </c>
       <c r="M211">
         <v>95</v>
@@ -36648,7 +36648,7 @@
         <v>15</v>
       </c>
       <c r="S233" t="s">
-        <v>427</v>
+        <v>629</v>
       </c>
       <c r="T233" t="s">
         <v>412</v>
@@ -36710,7 +36710,7 @@
         <v>15</v>
       </c>
       <c r="S234" t="s">
-        <v>629</v>
+        <v>427</v>
       </c>
       <c r="T234" t="s">
         <v>412</v>
@@ -37268,7 +37268,7 @@
         <v>15</v>
       </c>
       <c r="S243" t="s">
-        <v>629</v>
+        <v>427</v>
       </c>
       <c r="T243" t="s">
         <v>412</v>
@@ -37330,7 +37330,7 @@
         <v>15</v>
       </c>
       <c r="S244" t="s">
-        <v>427</v>
+        <v>629</v>
       </c>
       <c r="T244" t="s">
         <v>412</v>
@@ -38942,7 +38942,7 @@
         <v>15</v>
       </c>
       <c r="S270" t="s">
-        <v>629</v>
+        <v>427</v>
       </c>
       <c r="T270" t="s">
         <v>412</v>
@@ -39004,7 +39004,7 @@
         <v>15</v>
       </c>
       <c r="S271" t="s">
-        <v>427</v>
+        <v>629</v>
       </c>
       <c r="T271" t="s">
         <v>412</v>
@@ -43666,7 +43666,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A0A6AC0-0616-4AF0-BF0B-14A356C47FDB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2AC245-E562-4145-AC26-3B10D6322BE5}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_POL_grids_kan/vt_vervestacks_POL_v1.xlsx
+++ b/VerveStacks_POL_grids_kan/vt_vervestacks_POL_v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DBCC92B-3284-4C08-AF43-B59C8047F7FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B80263F-7E90-4A65-8E22-998486A76EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{950F7191-5807-4A64-8E99-3F55D24FFAE5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{BC1480B2-65F0-40DB-A14C-D91FC7FDC7B3}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -4111,7 +4111,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F844FB0E-1227-403A-9CA4-3BDAF8537147}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6FEFCE5-BB6E-4A92-9156-263C88D21D89}">
   <dimension ref="B9:V187"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15165,7 +15165,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B495903-5802-47A8-868A-7BB37DDF7883}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{290646EC-A32D-49DA-8EFB-DCD3BC4B7153}">
   <dimension ref="B9:W157"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23078,7 +23078,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5825902D-8C42-43F6-9989-4ACBB9DBA55D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D59E8E90-D17A-47E4-9CA7-B24082B45183}">
   <dimension ref="B9:W388"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -36648,7 +36648,7 @@
         <v>15</v>
       </c>
       <c r="S233" t="s">
-        <v>629</v>
+        <v>427</v>
       </c>
       <c r="T233" t="s">
         <v>412</v>
@@ -36710,7 +36710,7 @@
         <v>15</v>
       </c>
       <c r="S234" t="s">
-        <v>427</v>
+        <v>629</v>
       </c>
       <c r="T234" t="s">
         <v>412</v>
@@ -37268,7 +37268,7 @@
         <v>15</v>
       </c>
       <c r="S243" t="s">
-        <v>427</v>
+        <v>629</v>
       </c>
       <c r="T243" t="s">
         <v>412</v>
@@ -37330,7 +37330,7 @@
         <v>15</v>
       </c>
       <c r="S244" t="s">
-        <v>629</v>
+        <v>427</v>
       </c>
       <c r="T244" t="s">
         <v>412</v>
@@ -37454,7 +37454,7 @@
         <v>15</v>
       </c>
       <c r="S246" t="s">
-        <v>427</v>
+        <v>629</v>
       </c>
       <c r="T246" t="s">
         <v>412</v>
@@ -37516,7 +37516,7 @@
         <v>15</v>
       </c>
       <c r="S247" t="s">
-        <v>629</v>
+        <v>427</v>
       </c>
       <c r="T247" t="s">
         <v>412</v>
@@ -38942,7 +38942,7 @@
         <v>15</v>
       </c>
       <c r="S270" t="s">
-        <v>427</v>
+        <v>629</v>
       </c>
       <c r="T270" t="s">
         <v>412</v>
@@ -39004,7 +39004,7 @@
         <v>15</v>
       </c>
       <c r="S271" t="s">
-        <v>629</v>
+        <v>427</v>
       </c>
       <c r="T271" t="s">
         <v>412</v>
@@ -43666,7 +43666,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2AC245-E562-4145-AC26-3B10D6322BE5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A42C39FA-9AC3-4280-B6B0-E50C7E9B8ABC}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
